--- a/events/Montemor_2015_WC/Montemor_2015_WC_Results.xlsx
+++ b/events/Montemor_2015_WC/Montemor_2015_WC_Results.xlsx
@@ -1442,6 +1442,11 @@
           <t>0:04:17.216</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1621,6 +1626,11 @@
       <c r="L18" t="n">
         <v>8</v>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>60136</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -2130,6 +2140,11 @@
       <c r="L26" t="n">
         <v>1</v>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>60135</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -3609,6 +3624,11 @@
       <c r="L49" t="n">
         <v>5</v>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -5748,6 +5768,11 @@
           <t>54262</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>42165</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5797,6 +5822,16 @@
       <c r="L82" t="n">
         <v>3</v>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>54759</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>54762</t>
+        </is>
+      </c>
       <c r="X82" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -6442,6 +6477,11 @@
           <t>0:00:40.000</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7291,6 +7331,16 @@
       <c r="L105" t="n">
         <v>7</v>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>60130</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>60129</t>
+        </is>
+      </c>
       <c r="X105" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -8261,6 +8311,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8466,6 +8521,11 @@
           <t>52750</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9189,6 +9249,16 @@
       <c r="L133" t="n">
         <v>8</v>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>60130</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>60129</t>
+        </is>
+      </c>
       <c r="X133" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -10224,6 +10294,11 @@
           <t>0:04:24.556</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13279,6 +13354,11 @@
           <t>54262</t>
         </is>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>42165</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14629,6 +14709,11 @@
           <t>52750</t>
         </is>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -17954,6 +18039,11 @@
           <t>0:03:56.784</t>
         </is>
       </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -20051,6 +20141,11 @@
           <t>0:00:38.708</t>
         </is>
       </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -21368,6 +21463,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -21713,6 +21813,11 @@
           <t>52750</t>
         </is>
       </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -24426,6 +24531,11 @@
       <c r="L359" t="n">
         <v>6</v>
       </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
       <c r="X359" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -27201,6 +27311,11 @@
           <t>0:04:18.900</t>
         </is>
       </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -27250,6 +27365,11 @@
       <c r="L403" t="n">
         <v>5</v>
       </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
       <c r="X403" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -27600,6 +27720,11 @@
           <t>54770</t>
         </is>
       </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -27940,6 +28065,11 @@
           <t>60759</t>
         </is>
       </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -28350,6 +28480,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="U419" t="inlineStr">
         <is>
           <t>36450</t>
@@ -29125,6 +29260,11 @@
           <t>0:03:13.516</t>
         </is>
       </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
       <c r="T429" t="inlineStr">
         <is>
           <t>54773</t>
@@ -29995,6 +30135,11 @@
           <t>0:02:09.324</t>
         </is>
       </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -35430,6 +35575,11 @@
           <t>54770</t>
         </is>
       </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -36015,6 +36165,11 @@
           <t>0:02:58.912</t>
         </is>
       </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
       <c r="T529" t="inlineStr">
         <is>
           <t>54773</t>
@@ -36495,6 +36650,11 @@
           <t>0:04:13.628</t>
         </is>
       </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -36555,6 +36715,11 @@
           <t>0:01:53.036</t>
         </is>
       </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -39152,6 +39317,11 @@
           <t>54770</t>
         </is>
       </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -40244,6 +40414,11 @@
           <t>60759</t>
         </is>
       </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -40835,6 +41010,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="U600" t="inlineStr">
         <is>
           <t>36450</t>
@@ -41575,6 +41755,11 @@
           <t>0:01:48.172</t>
         </is>
       </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -45565,6 +45750,11 @@
           <t>52148</t>
         </is>
       </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="U665" t="inlineStr">
         <is>
           <t>54777</t>
@@ -46908,6 +47098,11 @@
           <t>0:27:44.540</t>
         </is>
       </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -46959,6 +47154,11 @@
       <c r="L685" t="n">
         <v>5</v>
       </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>61276</t>
+        </is>
+      </c>
       <c r="X685" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -47361,6 +47561,11 @@
           <t>0:23:31.570</t>
         </is>
       </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -47490,6 +47695,11 @@
           <t>0:23:58.260</t>
         </is>
       </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -48343,6 +48553,11 @@
       <c r="P706" t="inlineStr">
         <is>
           <t>0:20:55.990</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>106349</t>
         </is>
       </c>
     </row>
@@ -49009,7 +49224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D258"/>
+  <dimension ref="A1:D275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54688,6 +54903,380 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>42165</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ROBINSON</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Aleksandra</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>GORNA</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>54759</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Igor</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>PINHO</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>54762</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>BRITO</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>60129</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Tatiana</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>MUNOZ RUA</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>60130</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Adriana</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>PITA NINO</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>60135</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Johan</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>CANO GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>60136</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>DAVID DIAZ</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>61276</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>PINTO</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>CAMEIRA</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Adnan</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ALIEV</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Saeid</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>FAZLOULA</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Montemor_2015_WC/Montemor_2015_WC_Results.xlsx
+++ b/events/Montemor_2015_WC/Montemor_2015_WC_Results.xlsx
@@ -26481,6 +26481,11 @@
           <t>0:00:36.500</t>
         </is>
       </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>55865</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -34220,6 +34225,11 @@
           <t>0:00:38.200</t>
         </is>
       </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>55865</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -44352,6 +44362,11 @@
       <c r="P647" t="inlineStr">
         <is>
           <t>0:00:35.516</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>55865</t>
         </is>
       </c>
     </row>
@@ -49224,7 +49239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D275"/>
+  <dimension ref="A1:D276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55277,6 +55292,28 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>55865</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Sergei</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>TOKARNITSKYI</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
